--- a/data/main/sheets/batch_03.xlsx
+++ b/data/main/sheets/batch_03.xlsx
@@ -467,19 +467,19 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_356</t>
+          <t xml:space="preserve">multiple_162</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me a recipe that serves 2 people, is vegan, and takes under 30 minutes to prepare.</t>
+          <t xml:space="preserve">What is the structural dynamic analysis of the building with building Id B1004 for 2nd, 3rd and 4th floors?</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">servings = 2
-diet = vegan
-prep_time = 30</t>
+          <t xml:space="preserve">building_id = B1004
+floors = 2, 3, 4
+mode = dynamic</t>
         </is>
       </c>
       <c r="D3" s="6"/>
@@ -491,18 +491,19 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_19</t>
+          <t xml:space="preserve">simple_python_86</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What are the three great Schism in Christianity history?</t>
+          <t xml:space="preserve">Find the shortest distance between two cities, New York and Los Angeles, through the train and you can transfer.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">religion = Christianity
-count = three</t>
+          <t xml:space="preserve">start_city = New York
+end_city = Los Angeles
+transportation = train</t>
         </is>
       </c>
       <c r="D4" s="6"/>
@@ -514,19 +515,18 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_399</t>
+          <t xml:space="preserve">multiple_177</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me the best Italian restaurants in New York City with average customer ratings of more than 4 and accepts credit cards.</t>
+          <t xml:space="preserve">Find the top chess players in New York with a rating above 2300.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = New York City
-cuisine = Italian
-rating = 4</t>
+          <t xml:space="preserve">location = New York
+minimum_rating = 2300</t>
         </is>
       </c>
       <c r="D5" s="6"/>
@@ -538,19 +538,19 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_162</t>
+          <t xml:space="preserve">simple_python_91</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the structural dynamic analysis of the building with building Id B1004 for 2nd, 3rd and 4th floors?</t>
+          <t xml:space="preserve">Get the highest rated sushi restaurant in Boston, that opens on Sundays.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">building_id = B1004
-floors = 2, 3, 4
-mode = dynamic</t>
+          <t xml:space="preserve">cuisine = sushi
+location = Boston
+condition = opens on Sundays</t>
         </is>
       </c>
       <c r="D6" s="6"/>
@@ -562,20 +562,18 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_287</t>
+          <t xml:space="preserve">simple_python_59</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me a classical concert this weekend in Los Angeles with cheap tickets.</t>
+          <t xml:space="preserve">Calculate the molecular weight of Glucose (C6H12O6) in grams/mole.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">genre = classical
-location = Los Angeles
-date = this weekend
-price_range = cheap</t>
+          <t xml:space="preserve">compound = C6H12O6
+to_unit = grams/mole</t>
         </is>
       </c>
       <c r="D7" s="6"/>
@@ -587,18 +585,19 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_177</t>
+          <t xml:space="preserve">multiple_67</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the top chess players in New York with a rating above 2300.</t>
+          <t xml:space="preserve">Translate Hello, how are you? from English to French.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = New York
-minimum_rating = 2300</t>
+          <t xml:space="preserve">text = Hello, how are you?
+source_language = English
+target_language = French</t>
         </is>
       </c>
       <c r="D8" s="6"/>
@@ -610,19 +609,20 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_91</t>
+          <t xml:space="preserve">simple_python_125</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the highest rated sushi restaurant in Boston, that opens on Sundays.</t>
+          <t xml:space="preserve">Predict house price in San Francisco based on its area of 2500 square feet, number of rooms as 5 and year of construction is 1990.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuisine = sushi
-location = Boston
-condition = opens on Sundays</t>
+          <t xml:space="preserve">area = 2500
+rooms = 5
+year = 1990
+location = San Francisco</t>
         </is>
       </c>
       <c r="D9" s="6"/>
@@ -634,18 +634,19 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_59</t>
+          <t xml:space="preserve">multiple_52</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calculate the molecular weight of Glucose (C6H12O6) in grams/mole.</t>
+          <t xml:space="preserve">I have 100 euro. How much is it in USD?</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">compound = C6H12O6
-to_unit = grams/mole</t>
+          <t xml:space="preserve">amount = 100
+from_currency = euro
+to_currency = USD</t>
         </is>
       </c>
       <c r="D10" s="6"/>
@@ -657,19 +658,18 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_67</t>
+          <t xml:space="preserve">simple_python_270</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Translate Hello, how are you? from English to French.</t>
+          <t xml:space="preserve">Can you give me the height and width of Empire State building in feet?</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">text = Hello, how are you?
-source_language = English
-target_language = French</t>
+          <t xml:space="preserve">building_name = Empire State building
+unit = feet</t>
         </is>
       </c>
       <c r="D11" s="6"/>
@@ -681,22 +681,19 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_386</t>
+          <t xml:space="preserve">multiple_61</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book a luxury room in Hotel Paradise, Las Vegas, with a city view for 3 days starting from May 12, 2022.</t>
+          <t xml:space="preserve">Find a Landscape Architect who is experienced 5 years in small space garden design in Portland</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hotel_name = Hotel Paradise
-location = Las Vegas
-room_type = luxury
-start_date = May 12, 2022
-stay_duration = 3
-view = city view</t>
+          <t xml:space="preserve">location = Portland
+specialization = small space garden design
+years_experience = 5</t>
         </is>
       </c>
       <c r="D12" s="6"/>
@@ -708,19 +705,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_52</t>
+          <t xml:space="preserve">simple_python_241</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I have 100 euro. How much is it in USD?</t>
+          <t xml:space="preserve">Who was the U.S. president during the Civil War?</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">amount = 100
-from_currency = euro
-to_currency = USD</t>
+          <t xml:space="preserve">event = Civil War</t>
         </is>
       </c>
       <c r="D13" s="6"/>
@@ -732,18 +727,20 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_270</t>
+          <t xml:space="preserve">simple_python_173</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Can you give me the height and width of Empire State building in feet?</t>
+          <t xml:space="preserve">Find state law cases related to land disputes in the past 5 years from 2015 to 2021 in New York.</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">building_name = Empire State building
-unit = feet</t>
+          <t xml:space="preserve">topic = land disputes
+year_range = 2015, 2021
+location = New York
+judicial_system = state</t>
         </is>
       </c>
       <c r="D14" s="6"/>
@@ -755,19 +752,18 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_61</t>
+          <t xml:space="preserve">multiple_26</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find a Landscape Architect who is experienced 5 years in small space garden design in Portland</t>
+          <t xml:space="preserve">Find out the rewards for playing Fortnite on Playstation platform with different missions and trophies</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Portland
-specialization = small space garden design
-years_experience = 5</t>
+          <t xml:space="preserve">game = Fortnite
+platform = Playstation</t>
         </is>
       </c>
       <c r="D15" s="6"/>
@@ -779,17 +775,19 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_241</t>
+          <t xml:space="preserve">simple_python_396</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who was the U.S. president during the Civil War?</t>
+          <t xml:space="preserve">Find a hospital within 5 km radius around Denver, Colorado with pediatrics department.</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">event = Civil War</t>
+          <t xml:space="preserve">location = Denver, Colorado
+radius = 5
+department = pediatrics</t>
         </is>
       </c>
       <c r="D16" s="6"/>
@@ -801,20 +799,18 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_173</t>
+          <t xml:space="preserve">multiple_25</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find state law cases related to land disputes in the past 5 years from 2015 to 2021 in New York.</t>
+          <t xml:space="preserve">What is the cheapest selling price for the game 'Assassins Creed Valhalla' in the PlayStation Store in the United States?</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic = land disputes
-year_range = 2015, 2021
-location = New York
-judicial_system = state</t>
+          <t xml:space="preserve">game_title = Assassins Creed Valhalla
+platform = PlayStation</t>
         </is>
       </c>
       <c r="D17" s="6"/>
@@ -826,18 +822,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_26</t>
+          <t xml:space="preserve">simple_python_167</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find out the rewards for playing Fortnite on Playstation platform with different missions and trophies</t>
+          <t xml:space="preserve">Retrieve the details of a Supreme Court case titled 'Roe v. Wade'.Include dissent information.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game = Fortnite
-platform = Playstation</t>
+          <t xml:space="preserve">case_title = Roe v. Wade</t>
         </is>
       </c>
       <c r="D18" s="6"/>
@@ -849,19 +844,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_168</t>
+          <t xml:space="preserve">simple_python_274</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Search for ongoing lawsuits related to the company 'Google' filed after January 1, 2021 in California.</t>
+          <t xml:space="preserve">Find information about the opening hours of the Metropolitan Museum of Art.</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">company = Google
-start_date = January 1, 2021
-location = California</t>
+          <t xml:space="preserve">museum_name = the Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="D19" s="6"/>
@@ -873,18 +866,19 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_25</t>
+          <t xml:space="preserve">multiple_94</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What is the cheapest selling price for the game 'Assassins Creed Valhalla' in the PlayStation Store in the United States?</t>
+          <t xml:space="preserve">I want to book a suite with queen size bed for 3 nights in Hilton New York. Can you find the pricing for me?</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game_title = Assassins Creed Valhalla
-platform = PlayStation</t>
+          <t xml:space="preserve">hotelName = Hilton New York
+roomType = suite with queen size bed
+nights = 3</t>
         </is>
       </c>
       <c r="D20" s="6"/>
@@ -896,17 +890,18 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_167</t>
+          <t xml:space="preserve">simple_python_354</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retrieve the details of a Supreme Court case titled 'Roe v. Wade'.Include dissent information.</t>
+          <t xml:space="preserve">Find a vegan soup recipe that takes under 30 minutes to make.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">case_title = Roe v. Wade</t>
+          <t xml:space="preserve">dish_type = soup
+cooking_time = 30</t>
         </is>
       </c>
       <c r="D21" s="6"/>
@@ -918,17 +913,18 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_274</t>
+          <t xml:space="preserve">multiple_112</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find information about the opening hours of the Metropolitan Museum of Art.</t>
+          <t xml:space="preserve">Predict the growth of forest in Yellowstone National Park for the next 5 years including human impact.</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">museum_name = the Metropolitan Museum of Art</t>
+          <t xml:space="preserve">location = Yellowstone National Park
+years = 5</t>
         </is>
       </c>
       <c r="D22" s="6"/>
@@ -940,19 +936,18 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_94</t>
+          <t xml:space="preserve">simple_python_226</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I want to book a suite with queen size bed for 3 nights in Hilton New York. Can you find the pricing for me?</t>
+          <t xml:space="preserve">Find the compatibility score in percentage of Aries with Gemini.</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hotelName = Hilton New York
-roomType = suite with queen size bed
-nights = 3</t>
+          <t xml:space="preserve">sign1 = Aries
+sign2 = Gemini</t>
         </is>
       </c>
       <c r="D23" s="6"/>
@@ -964,18 +959,19 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_371</t>
+          <t xml:space="preserve">multiple_189</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check the price of tomatoes and lettuce at the Whole Foods in Los Angeles.</t>
+          <t xml:space="preserve">Convert time 3pm from New York time zone to London time zone.</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Los Angeles
-items = tomatoes, lettuce</t>
+          <t xml:space="preserve">time = 3pm
+from_timezone = New York
+to_timezone = London</t>
         </is>
       </c>
       <c r="D24" s="6"/>
@@ -987,18 +983,19 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_112</t>
+          <t xml:space="preserve">simple_python_211</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predict the growth of forest in Yellowstone National Park for the next 5 years including human impact.</t>
+          <t xml:space="preserve">Send an email to John Doe at john.doe@example.com with the subject 'Meeting' and body 'Let's meet at 10 AM tomorrow'.</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">location = Yellowstone National Park
-years = 5</t>
+          <t xml:space="preserve">to = john.doe@example.com
+subject = Meeting
+body = Let's meet at 10 AM tomorrow</t>
         </is>
       </c>
       <c r="D25" s="6"/>
@@ -1010,18 +1007,18 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_226</t>
+          <t xml:space="preserve">simple_python_397</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the compatibility score in percentage of Aries with Gemini.</t>
+          <t xml:space="preserve">Find the distance between New York and Boston, accounting for terrain.</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sign1 = Aries
-sign2 = Gemini</t>
+          <t xml:space="preserve">origin = New York
+destination = Boston</t>
         </is>
       </c>
       <c r="D26" s="6"/>
@@ -1033,19 +1030,18 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_189</t>
+          <t xml:space="preserve">multiple_74</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert time 3pm from New York time zone to London time zone.</t>
+          <t xml:space="preserve">Find the price of Van Gogh's painting 'Starry Night' on all auction platforms.</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">time = 3pm
-from_timezone = New York
-to_timezone = London</t>
+          <t xml:space="preserve">artwork_name = Starry Night
+artist = Van Gogh</t>
         </is>
       </c>
       <c r="D27" s="6"/>
@@ -1057,19 +1053,18 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_211</t>
+          <t xml:space="preserve">simple_python_392</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Send an email to John Doe at john.doe@example.com with the subject 'Meeting' and body 'Let's meet at 10 AM tomorrow'.</t>
+          <t xml:space="preserve">Get me the latest exchange rate from British Pounds to Japanese Yen.</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">to = john.doe@example.com
-subject = Meeting
-body = Let's meet at 10 AM tomorrow</t>
+          <t xml:space="preserve">source_currency = British Pounds
+target_currency = Japanese Yen</t>
         </is>
       </c>
       <c r="D28" s="6"/>
@@ -1081,18 +1076,17 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_397</t>
+          <t xml:space="preserve">multiple_158</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the distance between New York and Boston, accounting for terrain.</t>
+          <t xml:space="preserve">Get the biography and main contributions of Pope Innocent III.</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">origin = New York
-destination = Boston</t>
+          <t xml:space="preserve">papal_name = Pope Innocent III</t>
         </is>
       </c>
       <c r="D29" s="6"/>
@@ -1104,18 +1098,18 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_74</t>
+          <t xml:space="preserve">simple_python_249</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find the price of Van Gogh's painting 'Starry Night' on all auction platforms.</t>
+          <t xml:space="preserve">Tell me more about Christianity and its history till the 14th century</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">artwork_name = Starry Night
-artist = Van Gogh</t>
+          <t xml:space="preserve">religion = Christianity
+till_century = 14</t>
         </is>
       </c>
       <c r="D30" s="6"/>
@@ -1127,18 +1121,17 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_392</t>
+          <t xml:space="preserve">multiple_153</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get me the latest exchange rate from British Pounds to Japanese Yen.</t>
+          <t xml:space="preserve">When was the signing of the Treaty of Lisbon?</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">source_currency = British Pounds
-target_currency = Japanese Yen</t>
+          <t xml:space="preserve">event = signing of the Treaty of Lisbon</t>
         </is>
       </c>
       <c r="D31" s="6"/>
@@ -1150,17 +1143,20 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_158</t>
+          <t xml:space="preserve">simple_python_217</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get the biography and main contributions of Pope Innocent III.</t>
+          <t xml:space="preserve">Analyze my fMRI data in ~/data/myfMRI.nii from a multi-band sequence, that is smoothed at 6mm with an isotropic voxel size of 2mm.</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">papal_name = Pope Innocent III</t>
+          <t xml:space="preserve">data_source = ~/data/myfMRI.nii
+sequence_type = multi-band
+smooth = 6
+voxel_size = 2</t>
         </is>
       </c>
       <c r="D32" s="6"/>
@@ -1172,18 +1168,18 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_249</t>
+          <t xml:space="preserve">simple_python_346</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tell me more about Christianity and its history till the 14th century</t>
+          <t xml:space="preserve">Get all collectable items from the game 'Animal Crossing: New Horizons' during the Spring season.</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">religion = Christianity
-till_century = 14</t>
+          <t xml:space="preserve">game_name = Animal Crossing: New Horizons
+season = Spring</t>
         </is>
       </c>
       <c r="D33" s="6"/>
@@ -1195,17 +1191,21 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_153</t>
+          <t xml:space="preserve">multiple_190</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">When was the signing of the Treaty of Lisbon?</t>
+          <t xml:space="preserve">Book a single room for two nights at the Hilton Hotel in Chicago, starting from 10th December 2022.</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">event = signing of the Treaty of Lisbon</t>
+          <t xml:space="preserve">hotel_name = Hilton Hotel
+location = Chicago
+room_type = single
+start_date = 10th December 2022
+nights = two</t>
         </is>
       </c>
       <c r="D34" s="6"/>
@@ -1217,20 +1217,18 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_217</t>
+          <t xml:space="preserve">simple_python_190</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analyze my fMRI data in ~/data/myfMRI.nii from a multi-band sequence, that is smoothed at 6mm with an isotropic voxel size of 2mm.</t>
+          <t xml:space="preserve">What's the elevation and area of Yellowstone National Park?</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">data_source = ~/data/myfMRI.nii
-sequence_type = multi-band
-smooth = 6
-voxel_size = 2</t>
+          <t xml:space="preserve">park_name = Yellowstone National Park
+information = elevation, area</t>
         </is>
       </c>
       <c r="D35" s="6"/>
@@ -1242,18 +1240,17 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_346</t>
+          <t xml:space="preserve">multiple_160</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Get all collectable items from the game 'Animal Crossing: New Horizons' during the Spring season.</t>
+          <t xml:space="preserve">Find me the most recent art sculpture by James Plensa with detailed description.</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">game_name = Animal Crossing: New Horizons
-season = Spring</t>
+          <t xml:space="preserve">artist_name = James Plensa</t>
         </is>
       </c>
       <c r="D36" s="6"/>
@@ -1265,21 +1262,18 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_190</t>
+          <t xml:space="preserve">simple_python_282</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book a single room for two nights at the Hilton Hotel in Chicago, starting from 10th December 2022.</t>
+          <t xml:space="preserve">Find a Yamaha flute with the specifications of open hole, C foot, and silver headjoint available for sale.</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hotel_name = Hilton Hotel
-location = Chicago
-room_type = single
-start_date = 10th December 2022
-nights = two</t>
+          <t xml:space="preserve">brand = Yamaha
+specs = open hole, C foot, silver headjoint</t>
         </is>
       </c>
       <c r="D37" s="6"/>
@@ -1291,18 +1285,18 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_190</t>
+          <t xml:space="preserve">multiple_182</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">What's the elevation and area of Yellowstone National Park?</t>
+          <t xml:space="preserve">Find me a multiplayer game with rating above 4.5 and compatible with Windows 10.</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">park_name = Yellowstone National Park
-information = elevation, area</t>
+          <t xml:space="preserve">platform = Windows 10
+rating = 4.5</t>
         </is>
       </c>
       <c r="D38" s="6"/>
@@ -1314,17 +1308,17 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_160</t>
+          <t xml:space="preserve">simple_python_182</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me the most recent art sculpture by James Plensa with detailed description.</t>
+          <t xml:space="preserve">Retrieve all the lawsuit details for case number XYZ123.</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">artist_name = James Plensa</t>
+          <t xml:space="preserve">case_number = XYZ123</t>
         </is>
       </c>
       <c r="D39" s="6"/>
@@ -1336,18 +1330,18 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_282</t>
+          <t xml:space="preserve">simple_python_266</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find a Yamaha flute with the specifications of open hole, C foot, and silver headjoint available for sale.</t>
+          <t xml:space="preserve">What is the value of the sculpture 'The Thinker' by Rodin?</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand = Yamaha
-specs = open hole, C foot, silver headjoint</t>
+          <t xml:space="preserve">sculpture = The Thinker
+artist = Rodin</t>
         </is>
       </c>
       <c r="D40" s="6"/>
@@ -1359,18 +1353,18 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">multiple_182</t>
+          <t xml:space="preserve">multiple_71</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Find me a multiplayer game with rating above 4.5 and compatible with Windows 10.</t>
+          <t xml:space="preserve">How many veterans were there in the United States in the year 1954?</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">platform = Windows 10
-rating = 4.5</t>
+          <t xml:space="preserve">year = 1954
+category = veterans</t>
         </is>
       </c>
       <c r="D41" s="6"/>
@@ -1382,17 +1376,21 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple_python_182</t>
+          <t xml:space="preserve">simple_python_380</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retrieve all the lawsuit details for case number XYZ123.</t>
+          <t xml:space="preserve">Book a single room at a pet friendly hotel near Manhattan, New York for 3 nights starting from March 10th, 2023.</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">case_number = XYZ123</t>
+          <t xml:space="preserve">location = Manhattan, New York
+room_type = single
+duration = 3
+start_date = March 10th, 2023
+preferences = pet friendly</t>
         </is>
       </c>
       <c r="D42" s="6"/>
